--- a/data/templates/world_cup_odds_template.xlsx
+++ b/data/templates/world_cup_odds_template.xlsx
@@ -10,7 +10,7 @@
     <sheet name="odds" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'odds'!$A$1:$Q$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'odds'!$A$1:$T$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,10 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="38" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="44" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -532,12 +535,27 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>odds_timestamp</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>odds_source_url</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>source_quality</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:T1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>